--- a/01_プロジェクト/BUYMA購入者配布資料/BUYMA_国内買付管理表_購入者版.xlsx
+++ b/01_プロジェクト/BUYMA購入者配布資料/BUYMA_国内買付管理表_購入者版.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="国内買付管理" sheetId="1" r:id="Rb9ce6fcc7c81419e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="2" r:id="R4acefde0c66c4935"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="経費・精算明細" sheetId="3" r:id="R4427dbd1576a4493"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="国内買付管理" sheetId="1" r:id="Re91526407fc34e3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="2" r:id="R24a7bad47e194c48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="経費・精算明細" sheetId="3" r:id="R9dcd513c67d643ce"/>
   </x:sheets>
 </x:workbook>
 </file>
